--- a/MAJSushiConfig/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-immunization-recommendation-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-immunization-recommendation-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-immunization-recommendation-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -715,7 +715,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-vaccine-code-cis|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-vaccine-code-cis|0.1.0</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation</t>
@@ -724,7 +724,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.coding:translation.id</t>
@@ -1110,7 +1110,7 @@
     <t>ImmunizationRecommendation.recommendation.supportingImmunization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-immunization-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-immunization-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1129,7 +1129,7 @@
     <t>ImmunizationRecommendation.recommendation.supportingPatientInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1475,7 +1475,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="100.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="97.05859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1490,7 +1490,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="110.53125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="87.83203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="84.6328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
